--- a/servers/maze_main_server/conf.d/data/maze_skill_auto_release_v8【迷宫-技能-自动释放技能】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_auto_release_v8【迷宫-技能-自动释放技能】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B5A0523-4EDE-40E7-9906-096D44ADC8DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{349447E3-2CCD-44E2-BE88-7D0F9D5D9891}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_auto_release_v8" sheetId="1" r:id="rId1"/>
@@ -28,8 +28,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -1640,7 +1638,7 @@
         <v>1</v>
       </c>
       <c r="I5" s="12">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J5" s="12" t="s">
         <v>3</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_auto_release_v8【迷宫-技能-自动释放技能】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_auto_release_v8【迷宫-技能-自动释放技能】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ACDB0AE-9AB3-48E7-8D77-07AC8790D783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70D5CF5D-EF18-47BA-B39F-8278EC46B73E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_auto_release_v8" sheetId="7" r:id="rId1"/>
@@ -403,14 +403,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>攻击命中造成伤害前</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击命中造成伤害后</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>受到攻击伤害前</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -627,6 +619,14 @@
   </si>
   <si>
     <t>【技能效果】命中后</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通攻击命中造成伤害前</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通攻击命中造成伤害后</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1226,7 +1226,7 @@
         <v>27</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F2" s="8" t="s">
         <v>28</v>
@@ -1264,34 +1264,34 @@
         <v>4</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>53</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I3" s="8" t="s">
         <v>55</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K3" s="8" t="s">
         <v>25</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="M3" s="8" t="s">
         <v>24</v>
@@ -1311,34 +1311,34 @@
         <v>19</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>54</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I4" s="8" t="s">
         <v>56</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="K4" s="8" t="s">
         <v>18</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="N4" s="8" t="s">
         <v>16</v>
@@ -1358,10 +1358,10 @@
         <v>1</v>
       </c>
       <c r="E5" s="25" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G5" s="13">
         <v>-1</v>
@@ -1402,10 +1402,10 @@
         <v>10</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G6" s="12">
         <v>-1</v>
@@ -1446,10 +1446,10 @@
         <v>15</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G7" s="12">
         <v>-1</v>
@@ -1488,10 +1488,10 @@
         <v>15</v>
       </c>
       <c r="E8" s="25" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G8" s="12">
         <v>-1</v>
@@ -1530,10 +1530,10 @@
         <v>1</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G9" s="2">
         <v>-1</v>
@@ -1574,10 +1574,10 @@
         <v>6</v>
       </c>
       <c r="E10" s="26" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G10" s="2">
         <v>-1</v>
@@ -1618,10 +1618,10 @@
         <v>1</v>
       </c>
       <c r="E11" s="27" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G11" s="8">
         <v>-1</v>
@@ -1662,10 +1662,10 @@
         <v>2</v>
       </c>
       <c r="E12" s="27" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G12" s="8">
         <v>-1</v>
@@ -1706,10 +1706,10 @@
         <v>1</v>
       </c>
       <c r="E13" s="28" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G13" s="11">
         <v>-1</v>
@@ -1750,10 +1750,10 @@
         <v>6</v>
       </c>
       <c r="E14" s="28" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G14" s="11">
         <v>-1</v>
@@ -1794,10 +1794,10 @@
         <v>4</v>
       </c>
       <c r="E15" s="29" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G15" s="7">
         <v>-1</v>
@@ -1838,10 +1838,10 @@
         <v>0</v>
       </c>
       <c r="E16" s="29" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G16" s="7">
         <v>-1</v>
@@ -1882,10 +1882,10 @@
         <v>6</v>
       </c>
       <c r="E17" s="29" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G17" s="7">
         <v>-1</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="E18" s="29" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G18" s="7">
         <v>-1</v>
@@ -1970,10 +1970,10 @@
         <v>0</v>
       </c>
       <c r="E19" s="29" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G19" s="7">
         <v>-1</v>
@@ -2014,10 +2014,10 @@
         <v>7</v>
       </c>
       <c r="E20" s="29" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G20" s="7">
         <v>1</v>
@@ -2058,10 +2058,10 @@
         <v>1</v>
       </c>
       <c r="E21" s="30" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F21" s="18" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G21" s="10">
         <v>-1</v>
@@ -2102,10 +2102,10 @@
         <v>1</v>
       </c>
       <c r="E22" s="30" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F22" s="18" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G22" s="10">
         <v>-1</v>
@@ -2146,10 +2146,10 @@
         <v>10</v>
       </c>
       <c r="E23" s="30" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G23" s="10">
         <v>-1</v>
@@ -2190,10 +2190,10 @@
         <v>0</v>
       </c>
       <c r="E24" s="30" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F24" s="18" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G24" s="10">
         <v>-1</v>
@@ -2234,10 +2234,10 @@
         <v>1</v>
       </c>
       <c r="E25" s="31" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F25" s="19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G25" s="9">
         <v>-1</v>
@@ -2278,10 +2278,10 @@
         <v>2</v>
       </c>
       <c r="E26" s="31" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F26" s="19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G26" s="9">
         <v>-1</v>
@@ -2322,10 +2322,10 @@
         <v>2</v>
       </c>
       <c r="E27" s="31" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F27" s="19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G27" s="9">
         <v>-1</v>
@@ -2366,10 +2366,10 @@
         <v>2</v>
       </c>
       <c r="E28" s="31" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F28" s="19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G28" s="9">
         <v>-1</v>
@@ -2410,10 +2410,10 @@
         <v>6</v>
       </c>
       <c r="E29" s="31" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F29" s="19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G29" s="9">
         <v>-1</v>
@@ -2538,13 +2538,13 @@
         <v>97</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>65</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>93</v>
@@ -2869,7 +2869,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>5</v>
@@ -2878,10 +2878,10 @@
         <v>19</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H4" s="23" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
@@ -2890,10 +2890,10 @@
         <v>1</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>100</v>
+        <v>163</v>
       </c>
       <c r="H5" s="23" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -2902,7 +2902,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>101</v>
+        <v>164</v>
       </c>
       <c r="H6" s="23"/>
     </row>
@@ -2912,10 +2912,10 @@
         <v>3</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H7" s="24" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -2924,10 +2924,10 @@
         <v>4</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="H8" s="23" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
@@ -2936,7 +2936,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H9" s="23"/>
     </row>
@@ -2946,11 +2946,11 @@
         <v>6</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D10" s="22"/>
       <c r="H10" s="24" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -2959,11 +2959,11 @@
         <v>7</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D11" s="22"/>
       <c r="H11" s="23" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="C12" s="21"/>
       <c r="D12" s="21" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H12" s="23"/>
     </row>
@@ -2982,10 +2982,10 @@
         <v>9</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H13" s="24" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
@@ -2993,11 +2993,11 @@
         <v>10</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D14" s="22"/>
       <c r="H14" s="23" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
@@ -3005,7 +3005,7 @@
         <v>11</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H15" s="23"/>
     </row>
@@ -3014,7 +3014,7 @@
         <v>12</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="H16" s="23"/>
     </row>
@@ -3023,7 +3023,7 @@
         <v>13</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D17" s="22"/>
     </row>
@@ -3032,7 +3032,7 @@
         <v>14</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.2">
@@ -3040,7 +3040,7 @@
         <v>15</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.2">

--- a/servers/maze_main_server/conf.d/data/maze_skill_auto_release_v8【迷宫-技能-自动释放技能】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_auto_release_v8【迷宫-技能-自动释放技能】.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F767239B-05BE-48DD-8352-69AE6083ED9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B48C3F88-F1B7-4E54-AEC4-E573ACE181D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_auto_release_v8" sheetId="7" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="164">
   <si>
     <t>0:0</t>
   </si>
@@ -644,6 +644,10 @@
   </si>
   <si>
     <t>毫秒</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>普攻击中目标回复血量</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -651,7 +655,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1197,8 +1201,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F17C44E-7F43-4887-B69D-27FDC1ACC173}">
-  <dimension ref="A1:N28"/>
-  <sheetFormatPr defaultRowHeight="11.25"/>
+  <dimension ref="A1:N29"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="55.5" style="4" customWidth="1"/>
@@ -1217,7 +1221,7 @@
     <col min="15" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="13.5">
+    <row r="1" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A1" s="10" t="s">
         <v>30</v>
       </c>
@@ -1235,7 +1239,7 @@
       <c r="M1" s="10"/>
       <c r="N1" s="10"/>
     </row>
-    <row r="2" spans="1:14" ht="13.5">
+    <row r="2" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
@@ -1279,7 +1283,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="13.5">
+    <row r="3" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A3" s="18" t="s">
         <v>3</v>
       </c>
@@ -1323,7 +1327,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="13.5">
+    <row r="4" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A4" s="18" t="s">
         <v>20</v>
       </c>
@@ -1367,7 +1371,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="13.5">
+    <row r="5" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A5" s="19">
         <v>550001</v>
       </c>
@@ -1411,7 +1415,7 @@
         <v>5000001</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="13.5">
+    <row r="6" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A6" s="19">
         <v>550002</v>
       </c>
@@ -1455,7 +1459,7 @@
         <v>5000001</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="13.5">
+    <row r="7" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A7" s="19">
         <v>550003</v>
       </c>
@@ -1497,7 +1501,7 @@
       </c>
       <c r="N7" s="11"/>
     </row>
-    <row r="8" spans="1:14" ht="13.5">
+    <row r="8" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A8" s="19">
         <v>550004</v>
       </c>
@@ -1539,7 +1543,7 @@
       </c>
       <c r="N8" s="11"/>
     </row>
-    <row r="9" spans="1:14" ht="13.5">
+    <row r="9" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A9" s="21">
         <v>560001</v>
       </c>
@@ -1583,7 +1587,7 @@
         <v>6000001</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="13.5">
+    <row r="10" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A10" s="21">
         <v>560002</v>
       </c>
@@ -1627,7 +1631,7 @@
         <v>6010001</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="13.5">
+    <row r="11" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A11" s="10">
         <v>570001</v>
       </c>
@@ -1671,7 +1675,7 @@
         <v>7000001</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="13.5">
+    <row r="12" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A12" s="10">
         <v>570002</v>
       </c>
@@ -1715,7 +1719,7 @@
         <v>7010001</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="13.5">
+    <row r="13" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A13" s="22">
         <v>580001</v>
       </c>
@@ -1759,7 +1763,7 @@
         <v>8000001</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="13.5">
+    <row r="14" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A14" s="22">
         <v>580002</v>
       </c>
@@ -1803,7 +1807,7 @@
         <v>8010001</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="13.5">
+    <row r="15" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A15" s="23">
         <v>590001</v>
       </c>
@@ -1847,7 +1851,7 @@
         <v>59030001</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="13.5">
+    <row r="16" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A16" s="23">
         <v>590002</v>
       </c>
@@ -1891,7 +1895,7 @@
         <v>59200001</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="13.5">
+    <row r="17" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A17" s="23">
         <v>590003</v>
       </c>
@@ -1933,7 +1937,7 @@
         <v>59090001</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="13.5">
+    <row r="18" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A18" s="23">
         <v>590004</v>
       </c>
@@ -1977,7 +1981,7 @@
         <v>54080001</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="13.5">
+    <row r="19" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A19" s="23">
         <v>590005</v>
       </c>
@@ -2021,7 +2025,7 @@
         <v>59200001</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="13.5">
+    <row r="20" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A20" s="23">
         <v>590006</v>
       </c>
@@ -2063,7 +2067,7 @@
         <v>9000001</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="13.5">
+    <row r="21" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A21" s="24">
         <v>600001</v>
       </c>
@@ -2107,7 +2111,7 @@
         <v>60010001</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="13.5">
+    <row r="22" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A22" s="24">
         <v>600002</v>
       </c>
@@ -2151,7 +2155,7 @@
         <v>10010001</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="13.5">
+    <row r="23" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A23" s="24">
         <v>600003</v>
       </c>
@@ -2195,7 +2199,7 @@
         <v>10020001</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="13.5">
+    <row r="24" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A24" s="25">
         <v>610001</v>
       </c>
@@ -2239,7 +2243,7 @@
         <v>11010001</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="13.5">
+    <row r="25" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A25" s="25">
         <v>610002</v>
       </c>
@@ -2283,7 +2287,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="13.5">
+    <row r="26" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A26" s="25">
         <v>610003</v>
       </c>
@@ -2327,7 +2331,7 @@
         <v>11020001</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="13.5">
+    <row r="27" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A27" s="25">
         <v>610004</v>
       </c>
@@ -2371,7 +2375,7 @@
         <v>11020001</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="13.5">
+    <row r="28" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A28" s="25">
         <v>610005</v>
       </c>
@@ -2413,6 +2417,50 @@
       </c>
       <c r="N28" s="25">
         <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
+      <c r="A29" s="19">
+        <v>620001</v>
+      </c>
+      <c r="B29" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="C29" s="20">
+        <v>25</v>
+      </c>
+      <c r="D29" s="19">
+        <v>2</v>
+      </c>
+      <c r="E29" s="26" t="s">
+        <v>158</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="G29" s="19">
+        <v>-1</v>
+      </c>
+      <c r="H29" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="I29" s="19">
+        <v>100</v>
+      </c>
+      <c r="J29" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="K29" s="19">
+        <v>10000</v>
+      </c>
+      <c r="L29" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="M29" s="19">
+        <v>1</v>
+      </c>
+      <c r="N29" s="19">
+        <v>59130001</v>
       </c>
     </row>
   </sheetData>
@@ -2425,7 +2473,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B2AAA09-75EC-48D5-8256-7AA6949156E5}">
   <dimension ref="A1:L35"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.5" bestFit="1" customWidth="1"/>
@@ -2439,7 +2487,7 @@
     <col min="12" max="12" width="17.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>93</v>
       </c>
@@ -2447,7 +2495,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -2466,7 +2514,7 @@
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -2499,7 +2547,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>62</v>
       </c>
@@ -2534,7 +2582,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>62</v>
       </c>
@@ -2545,7 +2593,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>62</v>
       </c>
@@ -2556,7 +2604,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>62</v>
       </c>
@@ -2567,7 +2615,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>69</v>
       </c>
@@ -2578,7 +2626,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>62</v>
       </c>
@@ -2589,7 +2637,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>69</v>
       </c>
@@ -2600,7 +2648,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>62</v>
       </c>
@@ -2611,7 +2659,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>62</v>
       </c>
@@ -2622,7 +2670,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>62</v>
       </c>
@@ -2633,7 +2681,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>62</v>
       </c>
@@ -2644,7 +2692,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>62</v>
       </c>
@@ -2655,7 +2703,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>69</v>
       </c>
@@ -2666,7 +2714,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>69</v>
       </c>
@@ -2677,7 +2725,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>62</v>
       </c>
@@ -2688,7 +2736,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>69</v>
       </c>
@@ -2699,7 +2747,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>85</v>
       </c>
@@ -2710,7 +2758,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>85</v>
       </c>
@@ -2724,7 +2772,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>69</v>
       </c>
@@ -2738,7 +2786,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>62</v>
       </c>
@@ -2752,62 +2800,62 @@
         <v>74</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E24" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E25" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E26" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E27" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E28" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E29" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E30" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E31" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E32" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="33" spans="5:5">
+    <row r="33" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E33" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="34" spans="5:5">
+    <row r="34" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E34" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="35" spans="5:5">
+    <row r="35" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E35" s="1" t="s">
         <v>7</v>
       </c>
@@ -2821,13 +2869,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{709BED1B-30AA-4E74-9F53-FE374AA39847}">
   <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>161</v>
       </c>
@@ -2838,17 +2886,17 @@
         <v>162</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="5"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>101</v>
       </c>
@@ -2865,7 +2913,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
       <c r="B5" s="2">
         <v>1</v>
@@ -2877,7 +2925,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="6">
         <v>2</v>
@@ -2887,7 +2935,7 @@
       </c>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
       <c r="B7" s="2">
         <v>3</v>
@@ -2899,7 +2947,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="6">
         <v>4</v>
@@ -2911,7 +2959,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="2">
         <v>5</v>
@@ -2921,7 +2969,7 @@
       </c>
       <c r="H9" s="8"/>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
       <c r="B10" s="6">
         <v>6</v>
@@ -2934,7 +2982,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
       <c r="B11" s="6">
         <v>7</v>
@@ -2947,7 +2995,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
       <c r="B12" s="6">
         <v>8</v>
@@ -2958,7 +3006,7 @@
       </c>
       <c r="H12" s="8"/>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B13" s="2">
         <v>9</v>
       </c>
@@ -2969,7 +3017,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B14" s="6">
         <v>10</v>
       </c>
@@ -2981,7 +3029,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B15" s="2">
         <v>11</v>
       </c>
@@ -2990,7 +3038,7 @@
       </c>
       <c r="H15" s="8"/>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B16" s="2">
         <v>12</v>
       </c>
@@ -2999,7 +3047,7 @@
       </c>
       <c r="H16" s="8"/>
     </row>
-    <row r="17" spans="2:4">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B17" s="6">
         <v>13</v>
       </c>
@@ -3008,7 +3056,7 @@
       </c>
       <c r="D17" s="7"/>
     </row>
-    <row r="18" spans="2:4">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B18" s="2">
         <v>14</v>
       </c>
@@ -3016,7 +3064,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="19" spans="2:4">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B19" s="2">
         <v>15</v>
       </c>
@@ -3024,7 +3072,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="20" spans="2:4">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B20" s="2">
         <v>16</v>
       </c>
@@ -3035,7 +3083,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="21" spans="2:4">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B21" s="2">
         <v>17</v>
       </c>

--- a/servers/maze_main_server/conf.d/data/maze_skill_auto_release_v8【迷宫-技能-自动释放技能】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_auto_release_v8【迷宫-技能-自动释放技能】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B48C3F88-F1B7-4E54-AEC4-E573ACE181D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8DD3750-028C-4595-8394-E7AC9DA27C3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_auto_release_v8" sheetId="7" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="164">
   <si>
     <t>0:0</t>
   </si>
@@ -2432,8 +2432,8 @@
       <c r="D29" s="19">
         <v>2</v>
       </c>
-      <c r="E29" s="26" t="s">
-        <v>158</v>
+      <c r="E29" s="26">
+        <v>26010001</v>
       </c>
       <c r="F29" s="11" t="s">
         <v>108</v>
@@ -2460,7 +2460,7 @@
         <v>1</v>
       </c>
       <c r="N29" s="19">
-        <v>59130001</v>
+        <v>59260001</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_skill_auto_release_v8【迷宫-技能-自动释放技能】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_auto_release_v8【迷宫-技能-自动释放技能】.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8DD3750-028C-4595-8394-E7AC9DA27C3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F767239B-05BE-48DD-8352-69AE6083ED9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_auto_release_v8" sheetId="7" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="163">
   <si>
     <t>0:0</t>
   </si>
@@ -644,10 +644,6 @@
   </si>
   <si>
     <t>毫秒</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>普攻击中目标回复血量</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -655,7 +651,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1201,8 +1197,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F17C44E-7F43-4887-B69D-27FDC1ACC173}">
-  <dimension ref="A1:N29"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:N28"/>
+  <sheetFormatPr defaultRowHeight="11.25"/>
   <cols>
     <col min="1" max="1" width="20.5" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="55.5" style="4" customWidth="1"/>
@@ -1221,7 +1217,7 @@
     <col min="15" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:14" ht="13.5">
       <c r="A1" s="10" t="s">
         <v>30</v>
       </c>
@@ -1239,7 +1235,7 @@
       <c r="M1" s="10"/>
       <c r="N1" s="10"/>
     </row>
-    <row r="2" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:14" ht="13.5">
       <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
@@ -1283,7 +1279,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:14" ht="13.5">
       <c r="A3" s="18" t="s">
         <v>3</v>
       </c>
@@ -1327,7 +1323,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:14" ht="13.5">
       <c r="A4" s="18" t="s">
         <v>20</v>
       </c>
@@ -1371,7 +1367,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:14" ht="13.5">
       <c r="A5" s="19">
         <v>550001</v>
       </c>
@@ -1415,7 +1411,7 @@
         <v>5000001</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:14" ht="13.5">
       <c r="A6" s="19">
         <v>550002</v>
       </c>
@@ -1459,7 +1455,7 @@
         <v>5000001</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:14" ht="13.5">
       <c r="A7" s="19">
         <v>550003</v>
       </c>
@@ -1501,7 +1497,7 @@
       </c>
       <c r="N7" s="11"/>
     </row>
-    <row r="8" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:14" ht="13.5">
       <c r="A8" s="19">
         <v>550004</v>
       </c>
@@ -1543,7 +1539,7 @@
       </c>
       <c r="N8" s="11"/>
     </row>
-    <row r="9" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:14" ht="13.5">
       <c r="A9" s="21">
         <v>560001</v>
       </c>
@@ -1587,7 +1583,7 @@
         <v>6000001</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:14" ht="13.5">
       <c r="A10" s="21">
         <v>560002</v>
       </c>
@@ -1631,7 +1627,7 @@
         <v>6010001</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:14" ht="13.5">
       <c r="A11" s="10">
         <v>570001</v>
       </c>
@@ -1675,7 +1671,7 @@
         <v>7000001</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:14" ht="13.5">
       <c r="A12" s="10">
         <v>570002</v>
       </c>
@@ -1719,7 +1715,7 @@
         <v>7010001</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:14" ht="13.5">
       <c r="A13" s="22">
         <v>580001</v>
       </c>
@@ -1763,7 +1759,7 @@
         <v>8000001</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:14" ht="13.5">
       <c r="A14" s="22">
         <v>580002</v>
       </c>
@@ -1807,7 +1803,7 @@
         <v>8010001</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:14" ht="13.5">
       <c r="A15" s="23">
         <v>590001</v>
       </c>
@@ -1851,7 +1847,7 @@
         <v>59030001</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:14" ht="13.5">
       <c r="A16" s="23">
         <v>590002</v>
       </c>
@@ -1895,7 +1891,7 @@
         <v>59200001</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:14" ht="13.5">
       <c r="A17" s="23">
         <v>590003</v>
       </c>
@@ -1937,7 +1933,7 @@
         <v>59090001</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:14" ht="13.5">
       <c r="A18" s="23">
         <v>590004</v>
       </c>
@@ -1981,7 +1977,7 @@
         <v>54080001</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:14" ht="13.5">
       <c r="A19" s="23">
         <v>590005</v>
       </c>
@@ -2025,7 +2021,7 @@
         <v>59200001</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:14" ht="13.5">
       <c r="A20" s="23">
         <v>590006</v>
       </c>
@@ -2067,7 +2063,7 @@
         <v>9000001</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:14" ht="13.5">
       <c r="A21" s="24">
         <v>600001</v>
       </c>
@@ -2111,7 +2107,7 @@
         <v>60010001</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:14" ht="13.5">
       <c r="A22" s="24">
         <v>600002</v>
       </c>
@@ -2155,7 +2151,7 @@
         <v>10010001</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:14" ht="13.5">
       <c r="A23" s="24">
         <v>600003</v>
       </c>
@@ -2199,7 +2195,7 @@
         <v>10020001</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:14" ht="13.5">
       <c r="A24" s="25">
         <v>610001</v>
       </c>
@@ -2243,7 +2239,7 @@
         <v>11010001</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:14" ht="13.5">
       <c r="A25" s="25">
         <v>610002</v>
       </c>
@@ -2287,7 +2283,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:14" ht="13.5">
       <c r="A26" s="25">
         <v>610003</v>
       </c>
@@ -2331,7 +2327,7 @@
         <v>11020001</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:14" ht="13.5">
       <c r="A27" s="25">
         <v>610004</v>
       </c>
@@ -2375,7 +2371,7 @@
         <v>11020001</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:14" ht="13.5">
       <c r="A28" s="25">
         <v>610005</v>
       </c>
@@ -2417,50 +2413,6 @@
       </c>
       <c r="N28" s="25">
         <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A29" s="19">
-        <v>620001</v>
-      </c>
-      <c r="B29" s="20" t="s">
-        <v>163</v>
-      </c>
-      <c r="C29" s="20">
-        <v>25</v>
-      </c>
-      <c r="D29" s="19">
-        <v>2</v>
-      </c>
-      <c r="E29" s="26">
-        <v>26010001</v>
-      </c>
-      <c r="F29" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="G29" s="19">
-        <v>-1</v>
-      </c>
-      <c r="H29" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="I29" s="19">
-        <v>100</v>
-      </c>
-      <c r="J29" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="K29" s="19">
-        <v>10000</v>
-      </c>
-      <c r="L29" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="M29" s="19">
-        <v>1</v>
-      </c>
-      <c r="N29" s="19">
-        <v>59260001</v>
       </c>
     </row>
   </sheetData>
@@ -2473,7 +2425,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B2AAA09-75EC-48D5-8256-7AA6949156E5}">
   <dimension ref="A1:L35"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="18.25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.5" bestFit="1" customWidth="1"/>
@@ -2487,7 +2439,7 @@
     <col min="12" max="12" width="17.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12">
       <c r="A1" s="2" t="s">
         <v>93</v>
       </c>
@@ -2495,7 +2447,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -2514,7 +2466,7 @@
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -2547,7 +2499,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12">
       <c r="A4" s="3" t="s">
         <v>62</v>
       </c>
@@ -2582,7 +2534,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12">
       <c r="A5" s="3" t="s">
         <v>62</v>
       </c>
@@ -2593,7 +2545,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12">
       <c r="A6" s="3" t="s">
         <v>62</v>
       </c>
@@ -2604,7 +2556,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12">
       <c r="A7" s="3" t="s">
         <v>62</v>
       </c>
@@ -2615,7 +2567,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12">
       <c r="A8" s="3" t="s">
         <v>69</v>
       </c>
@@ -2626,7 +2578,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12">
       <c r="A9" s="3" t="s">
         <v>62</v>
       </c>
@@ -2637,7 +2589,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12">
       <c r="A10" s="3" t="s">
         <v>69</v>
       </c>
@@ -2648,7 +2600,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12">
       <c r="A11" s="3" t="s">
         <v>62</v>
       </c>
@@ -2659,7 +2611,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12">
       <c r="A12" s="3" t="s">
         <v>62</v>
       </c>
@@ -2670,7 +2622,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12">
       <c r="A13" s="3" t="s">
         <v>62</v>
       </c>
@@ -2681,7 +2633,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12">
       <c r="A14" s="3" t="s">
         <v>62</v>
       </c>
@@ -2692,7 +2644,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12">
       <c r="A15" s="3" t="s">
         <v>62</v>
       </c>
@@ -2703,7 +2655,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12">
       <c r="A16" s="3" t="s">
         <v>69</v>
       </c>
@@ -2714,7 +2666,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5">
       <c r="A17" s="3" t="s">
         <v>69</v>
       </c>
@@ -2725,7 +2677,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5">
       <c r="A18" s="3" t="s">
         <v>62</v>
       </c>
@@ -2736,7 +2688,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5">
       <c r="A19" s="3" t="s">
         <v>69</v>
       </c>
@@ -2747,7 +2699,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5">
       <c r="A20" s="3" t="s">
         <v>85</v>
       </c>
@@ -2758,7 +2710,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5">
       <c r="A21" s="3" t="s">
         <v>85</v>
       </c>
@@ -2772,7 +2724,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5">
       <c r="A22" s="3" t="s">
         <v>69</v>
       </c>
@@ -2786,7 +2738,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5">
       <c r="A23" s="3" t="s">
         <v>62</v>
       </c>
@@ -2800,62 +2752,62 @@
         <v>74</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5">
       <c r="E24" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5">
       <c r="E25" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5">
       <c r="E26" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5">
       <c r="E27" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5">
       <c r="E28" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5">
       <c r="E29" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5">
       <c r="E30" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5">
       <c r="E31" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5">
       <c r="E32" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="33" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="5:5">
       <c r="E33" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="34" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="5:5">
       <c r="E34" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="35" spans="5:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="5:5">
       <c r="E35" s="1" t="s">
         <v>7</v>
       </c>
@@ -2869,13 +2821,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{709BED1B-30AA-4E74-9F53-FE374AA39847}">
   <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8">
       <c r="A1" s="2" t="s">
         <v>161</v>
       </c>
@@ -2886,17 +2838,17 @@
         <v>162</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8">
       <c r="A3" s="5"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
         <v>101</v>
       </c>
@@ -2913,7 +2865,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8">
       <c r="A5" s="2"/>
       <c r="B5" s="2">
         <v>1</v>
@@ -2925,7 +2877,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8">
       <c r="A6" s="2"/>
       <c r="B6" s="6">
         <v>2</v>
@@ -2935,7 +2887,7 @@
       </c>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8">
       <c r="A7" s="2"/>
       <c r="B7" s="2">
         <v>3</v>
@@ -2947,7 +2899,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8">
       <c r="A8" s="2"/>
       <c r="B8" s="6">
         <v>4</v>
@@ -2959,7 +2911,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8">
       <c r="A9" s="2"/>
       <c r="B9" s="2">
         <v>5</v>
@@ -2969,7 +2921,7 @@
       </c>
       <c r="H9" s="8"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8">
       <c r="A10" s="2"/>
       <c r="B10" s="6">
         <v>6</v>
@@ -2982,7 +2934,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8">
       <c r="A11" s="2"/>
       <c r="B11" s="6">
         <v>7</v>
@@ -2995,7 +2947,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8">
       <c r="A12" s="2"/>
       <c r="B12" s="6">
         <v>8</v>
@@ -3006,7 +2958,7 @@
       </c>
       <c r="H12" s="8"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8">
       <c r="B13" s="2">
         <v>9</v>
       </c>
@@ -3017,7 +2969,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8">
       <c r="B14" s="6">
         <v>10</v>
       </c>
@@ -3029,7 +2981,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8">
       <c r="B15" s="2">
         <v>11</v>
       </c>
@@ -3038,7 +2990,7 @@
       </c>
       <c r="H15" s="8"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8">
       <c r="B16" s="2">
         <v>12</v>
       </c>
@@ -3047,7 +2999,7 @@
       </c>
       <c r="H16" s="8"/>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:4">
       <c r="B17" s="6">
         <v>13</v>
       </c>
@@ -3056,7 +3008,7 @@
       </c>
       <c r="D17" s="7"/>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:4">
       <c r="B18" s="2">
         <v>14</v>
       </c>
@@ -3064,7 +3016,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:4">
       <c r="B19" s="2">
         <v>15</v>
       </c>
@@ -3072,7 +3024,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:4">
       <c r="B20" s="2">
         <v>16</v>
       </c>
@@ -3083,7 +3035,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:4">
       <c r="B21" s="2">
         <v>17</v>
       </c>

--- a/servers/maze_main_server/conf.d/data/maze_skill_auto_release_v8【迷宫-技能-自动释放技能】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_auto_release_v8【迷宫-技能-自动释放技能】.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F767239B-05BE-48DD-8352-69AE6083ED9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8DD3750-028C-4595-8394-E7AC9DA27C3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_auto_release_v8" sheetId="7" r:id="rId1"/>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="164">
   <si>
     <t>0:0</t>
   </si>
@@ -644,6 +644,10 @@
   </si>
   <si>
     <t>毫秒</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>普攻击中目标回复血量</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -651,7 +655,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1197,8 +1201,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F17C44E-7F43-4887-B69D-27FDC1ACC173}">
-  <dimension ref="A1:N28"/>
-  <sheetFormatPr defaultRowHeight="11.25"/>
+  <dimension ref="A1:N29"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="55.5" style="4" customWidth="1"/>
@@ -1217,7 +1221,7 @@
     <col min="15" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="13.5">
+    <row r="1" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A1" s="10" t="s">
         <v>30</v>
       </c>
@@ -1235,7 +1239,7 @@
       <c r="M1" s="10"/>
       <c r="N1" s="10"/>
     </row>
-    <row r="2" spans="1:14" ht="13.5">
+    <row r="2" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
@@ -1279,7 +1283,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="13.5">
+    <row r="3" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A3" s="18" t="s">
         <v>3</v>
       </c>
@@ -1323,7 +1327,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="13.5">
+    <row r="4" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A4" s="18" t="s">
         <v>20</v>
       </c>
@@ -1367,7 +1371,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="13.5">
+    <row r="5" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A5" s="19">
         <v>550001</v>
       </c>
@@ -1411,7 +1415,7 @@
         <v>5000001</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="13.5">
+    <row r="6" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A6" s="19">
         <v>550002</v>
       </c>
@@ -1455,7 +1459,7 @@
         <v>5000001</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="13.5">
+    <row r="7" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A7" s="19">
         <v>550003</v>
       </c>
@@ -1497,7 +1501,7 @@
       </c>
       <c r="N7" s="11"/>
     </row>
-    <row r="8" spans="1:14" ht="13.5">
+    <row r="8" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A8" s="19">
         <v>550004</v>
       </c>
@@ -1539,7 +1543,7 @@
       </c>
       <c r="N8" s="11"/>
     </row>
-    <row r="9" spans="1:14" ht="13.5">
+    <row r="9" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A9" s="21">
         <v>560001</v>
       </c>
@@ -1583,7 +1587,7 @@
         <v>6000001</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="13.5">
+    <row r="10" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A10" s="21">
         <v>560002</v>
       </c>
@@ -1627,7 +1631,7 @@
         <v>6010001</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="13.5">
+    <row r="11" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A11" s="10">
         <v>570001</v>
       </c>
@@ -1671,7 +1675,7 @@
         <v>7000001</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="13.5">
+    <row r="12" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A12" s="10">
         <v>570002</v>
       </c>
@@ -1715,7 +1719,7 @@
         <v>7010001</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="13.5">
+    <row r="13" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A13" s="22">
         <v>580001</v>
       </c>
@@ -1759,7 +1763,7 @@
         <v>8000001</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="13.5">
+    <row r="14" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A14" s="22">
         <v>580002</v>
       </c>
@@ -1803,7 +1807,7 @@
         <v>8010001</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="13.5">
+    <row r="15" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A15" s="23">
         <v>590001</v>
       </c>
@@ -1847,7 +1851,7 @@
         <v>59030001</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="13.5">
+    <row r="16" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A16" s="23">
         <v>590002</v>
       </c>
@@ -1891,7 +1895,7 @@
         <v>59200001</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="13.5">
+    <row r="17" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A17" s="23">
         <v>590003</v>
       </c>
@@ -1933,7 +1937,7 @@
         <v>59090001</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="13.5">
+    <row r="18" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A18" s="23">
         <v>590004</v>
       </c>
@@ -1977,7 +1981,7 @@
         <v>54080001</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="13.5">
+    <row r="19" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A19" s="23">
         <v>590005</v>
       </c>
@@ -2021,7 +2025,7 @@
         <v>59200001</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="13.5">
+    <row r="20" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A20" s="23">
         <v>590006</v>
       </c>
@@ -2063,7 +2067,7 @@
         <v>9000001</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="13.5">
+    <row r="21" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A21" s="24">
         <v>600001</v>
       </c>
@@ -2107,7 +2111,7 @@
         <v>60010001</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="13.5">
+    <row r="22" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A22" s="24">
         <v>600002</v>
       </c>
@@ -2151,7 +2155,7 @@
         <v>10010001</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="13.5">
+    <row r="23" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A23" s="24">
         <v>600003</v>
       </c>
@@ -2195,7 +2199,7 @@
         <v>10020001</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="13.5">
+    <row r="24" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A24" s="25">
         <v>610001</v>
       </c>
@@ -2239,7 +2243,7 @@
         <v>11010001</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="13.5">
+    <row r="25" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A25" s="25">
         <v>610002</v>
       </c>
@@ -2283,7 +2287,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="13.5">
+    <row r="26" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A26" s="25">
         <v>610003</v>
       </c>
@@ -2327,7 +2331,7 @@
         <v>11020001</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="13.5">
+    <row r="27" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A27" s="25">
         <v>610004</v>
       </c>
@@ -2371,7 +2375,7 @@
         <v>11020001</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="13.5">
+    <row r="28" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A28" s="25">
         <v>610005</v>
       </c>
@@ -2413,6 +2417,50 @@
       </c>
       <c r="N28" s="25">
         <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
+      <c r="A29" s="19">
+        <v>620001</v>
+      </c>
+      <c r="B29" s="20" t="s">
+        <v>163</v>
+      </c>
+      <c r="C29" s="20">
+        <v>25</v>
+      </c>
+      <c r="D29" s="19">
+        <v>2</v>
+      </c>
+      <c r="E29" s="26">
+        <v>26010001</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="G29" s="19">
+        <v>-1</v>
+      </c>
+      <c r="H29" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="I29" s="19">
+        <v>100</v>
+      </c>
+      <c r="J29" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="K29" s="19">
+        <v>10000</v>
+      </c>
+      <c r="L29" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="M29" s="19">
+        <v>1</v>
+      </c>
+      <c r="N29" s="19">
+        <v>59260001</v>
       </c>
     </row>
   </sheetData>
@@ -2425,7 +2473,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B2AAA09-75EC-48D5-8256-7AA6949156E5}">
   <dimension ref="A1:L35"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29.5" bestFit="1" customWidth="1"/>
@@ -2439,7 +2487,7 @@
     <col min="12" max="12" width="17.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>93</v>
       </c>
@@ -2447,7 +2495,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -2466,7 +2514,7 @@
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -2499,7 +2547,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>62</v>
       </c>
@@ -2534,7 +2582,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>62</v>
       </c>
@@ -2545,7 +2593,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>62</v>
       </c>
@@ -2556,7 +2604,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>62</v>
       </c>
@@ -2567,7 +2615,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>69</v>
       </c>
@@ -2578,7 +2626,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>62</v>
       </c>
@@ -2589,7 +2637,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>69</v>
       </c>
@@ -2600,7 +2648,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>62</v>
       </c>
@@ -2611,7 +2659,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>62</v>
       </c>
@@ -2622,7 +2670,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>62</v>
       </c>
@@ -2633,7 +2681,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>62</v>
       </c>
@@ -2644,7 +2692,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>62</v>
       </c>
@@ -2655,7 +2703,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>69</v>
       </c>
@@ -2666,7 +2714,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>69</v>
       </c>
@@ -2677,7 +2725,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>62</v>
       </c>
@@ -2688,7 +2736,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>69</v>
       </c>
@@ -2699,7 +2747,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
         <v>85</v>
       </c>
@@ -2710,7 +2758,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
         <v>85</v>
       </c>
@@ -2724,7 +2772,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>69</v>
       </c>
@@ -2738,7 +2786,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>62</v>
       </c>
@@ -2752,62 +2800,62 @@
         <v>74</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E24" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E25" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E26" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E27" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E28" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E29" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E30" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E31" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E32" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="33" spans="5:5">
+    <row r="33" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E33" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="34" spans="5:5">
+    <row r="34" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E34" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="35" spans="5:5">
+    <row r="35" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E35" s="1" t="s">
         <v>7</v>
       </c>
@@ -2821,13 +2869,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{709BED1B-30AA-4E74-9F53-FE374AA39847}">
   <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>161</v>
       </c>
@@ -2838,17 +2886,17 @@
         <v>162</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="2"/>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="5"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>101</v>
       </c>
@@ -2865,7 +2913,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
       <c r="B5" s="2">
         <v>1</v>
@@ -2877,7 +2925,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="6">
         <v>2</v>
@@ -2887,7 +2935,7 @@
       </c>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
       <c r="B7" s="2">
         <v>3</v>
@@ -2899,7 +2947,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="6">
         <v>4</v>
@@ -2911,7 +2959,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="2">
         <v>5</v>
@@ -2921,7 +2969,7 @@
       </c>
       <c r="H9" s="8"/>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
       <c r="B10" s="6">
         <v>6</v>
@@ -2934,7 +2982,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
       <c r="B11" s="6">
         <v>7</v>
@@ -2947,7 +2995,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
       <c r="B12" s="6">
         <v>8</v>
@@ -2958,7 +3006,7 @@
       </c>
       <c r="H12" s="8"/>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B13" s="2">
         <v>9</v>
       </c>
@@ -2969,7 +3017,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B14" s="6">
         <v>10</v>
       </c>
@@ -2981,7 +3029,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B15" s="2">
         <v>11</v>
       </c>
@@ -2990,7 +3038,7 @@
       </c>
       <c r="H15" s="8"/>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B16" s="2">
         <v>12</v>
       </c>
@@ -2999,7 +3047,7 @@
       </c>
       <c r="H16" s="8"/>
     </row>
-    <row r="17" spans="2:4">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B17" s="6">
         <v>13</v>
       </c>
@@ -3008,7 +3056,7 @@
       </c>
       <c r="D17" s="7"/>
     </row>
-    <row r="18" spans="2:4">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B18" s="2">
         <v>14</v>
       </c>
@@ -3016,7 +3064,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="19" spans="2:4">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B19" s="2">
         <v>15</v>
       </c>
@@ -3024,7 +3072,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="20" spans="2:4">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B20" s="2">
         <v>16</v>
       </c>
@@ -3035,7 +3083,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="21" spans="2:4">
+    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B21" s="2">
         <v>17</v>
       </c>

--- a/servers/maze_main_server/conf.d/data/maze_skill_auto_release_v8【迷宫-技能-自动释放技能】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_auto_release_v8【迷宫-技能-自动释放技能】.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8DD3750-028C-4595-8394-E7AC9DA27C3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5123CCE5-3072-4D38-8F21-9B7A2EB06F1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_auto_release_v8" sheetId="7" r:id="rId1"/>
@@ -647,7 +647,19 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>普攻击中目标回复血量</t>
+    <r>
+      <t>普攻击中目标回复血量</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（在用）</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -750,7 +762,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -808,6 +820,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -860,7 +878,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -917,6 +935,9 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="2" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2423,7 +2444,7 @@
       <c r="A29" s="19">
         <v>620001</v>
       </c>
-      <c r="B29" s="20" t="s">
+      <c r="B29" s="33" t="s">
         <v>163</v>
       </c>
       <c r="C29" s="20">

--- a/servers/maze_main_server/conf.d/data/maze_skill_auto_release_v8【迷宫-技能-自动释放技能】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_auto_release_v8【迷宫-技能-自动释放技能】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5123CCE5-3072-4D38-8F21-9B7A2EB06F1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09D4A967-D050-41BC-9ECC-1CA35B930FB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -67,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="168">
   <si>
     <t>0:0</t>
   </si>
@@ -660,6 +660,22 @@
       </rPr>
       <t>（在用）</t>
     </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>普攻击中目标触发寒霜</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>普攻击中目标触发燃烧</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>普攻击中目标触发概率冰冻</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>普攻击中目标触发概率麻痹</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1222,7 +1238,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F17C44E-7F43-4887-B69D-27FDC1ACC173}">
-  <dimension ref="A1:N29"/>
+  <dimension ref="A1:N33"/>
   <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="20.5" style="4" bestFit="1" customWidth="1"/>
@@ -2482,6 +2498,172 @@
       </c>
       <c r="N29" s="19">
         <v>59260001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
+      <c r="A30" s="19">
+        <v>630001</v>
+      </c>
+      <c r="B30" s="33" t="s">
+        <v>166</v>
+      </c>
+      <c r="C30" s="20"/>
+      <c r="D30" s="19">
+        <v>2</v>
+      </c>
+      <c r="E30" s="26">
+        <v>26010002</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="G30" s="19">
+        <v>-1</v>
+      </c>
+      <c r="H30" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="I30" s="19">
+        <v>0</v>
+      </c>
+      <c r="J30" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="K30" s="19">
+        <v>10000</v>
+      </c>
+      <c r="L30" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="M30" s="19">
+        <v>1</v>
+      </c>
+      <c r="N30" s="19">
+        <v>95001500</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
+      <c r="A31" s="19">
+        <v>630002</v>
+      </c>
+      <c r="B31" s="33" t="s">
+        <v>164</v>
+      </c>
+      <c r="C31" s="20"/>
+      <c r="D31" s="19">
+        <v>2</v>
+      </c>
+      <c r="E31" s="26">
+        <v>26010003</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="G31" s="19">
+        <v>-1</v>
+      </c>
+      <c r="H31" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="I31" s="19">
+        <v>0</v>
+      </c>
+      <c r="J31" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="K31" s="19">
+        <v>10000</v>
+      </c>
+      <c r="L31" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="M31" s="19">
+        <v>1</v>
+      </c>
+      <c r="N31" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
+      <c r="A32" s="19">
+        <v>640001</v>
+      </c>
+      <c r="B32" s="33" t="s">
+        <v>165</v>
+      </c>
+      <c r="D32" s="19">
+        <v>2</v>
+      </c>
+      <c r="E32" s="26">
+        <v>26010004</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="G32" s="19">
+        <v>-1</v>
+      </c>
+      <c r="H32" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="I32" s="19">
+        <v>0</v>
+      </c>
+      <c r="J32" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="K32" s="19">
+        <v>10000</v>
+      </c>
+      <c r="L32" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="M32" s="19">
+        <v>1</v>
+      </c>
+      <c r="N32" s="19">
+        <v>95101100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="13.5" x14ac:dyDescent="0.15">
+      <c r="A33" s="19">
+        <v>660001</v>
+      </c>
+      <c r="B33" s="33" t="s">
+        <v>167</v>
+      </c>
+      <c r="D33" s="19">
+        <v>2</v>
+      </c>
+      <c r="E33" s="26">
+        <v>26010004</v>
+      </c>
+      <c r="F33" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="G33" s="19">
+        <v>-1</v>
+      </c>
+      <c r="H33" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="I33" s="19">
+        <v>0</v>
+      </c>
+      <c r="J33" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="K33" s="19">
+        <v>10000</v>
+      </c>
+      <c r="L33" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="M33" s="19">
+        <v>1</v>
+      </c>
+      <c r="N33" s="19">
+        <v>95200700</v>
       </c>
     </row>
   </sheetData>

--- a/servers/maze_main_server/conf.d/data/maze_skill_auto_release_v8【迷宫-技能-自动释放技能】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_auto_release_v8【迷宫-技能-自动释放技能】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09D4A967-D050-41BC-9ECC-1CA35B930FB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F6253B5-5B65-4568-A80D-816F45BA1DD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -663,19 +663,67 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>普攻击中目标触发寒霜</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>普攻击中目标触发燃烧</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>普攻击中目标触发概率冰冻</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>普攻击中目标触发概率麻痹</t>
+    <r>
+      <t>普攻击中目标触发概率冰冻</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（废弃）</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>普攻击中目标触发概率麻痹</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（废弃）</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>普攻击中目标触发燃烧</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（废弃）</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>普攻击中目标触发寒霜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（废弃）</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -778,7 +826,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -842,6 +890,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -894,7 +948,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -953,6 +1007,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2504,8 +2561,8 @@
       <c r="A30" s="19">
         <v>630001</v>
       </c>
-      <c r="B30" s="33" t="s">
-        <v>166</v>
+      <c r="B30" s="34" t="s">
+        <v>164</v>
       </c>
       <c r="C30" s="20"/>
       <c r="D30" s="19">
@@ -2546,8 +2603,8 @@
       <c r="A31" s="19">
         <v>630002</v>
       </c>
-      <c r="B31" s="33" t="s">
-        <v>164</v>
+      <c r="B31" s="34" t="s">
+        <v>167</v>
       </c>
       <c r="C31" s="20"/>
       <c r="D31" s="19">
@@ -2588,8 +2645,8 @@
       <c r="A32" s="19">
         <v>640001</v>
       </c>
-      <c r="B32" s="33" t="s">
-        <v>165</v>
+      <c r="B32" s="34" t="s">
+        <v>166</v>
       </c>
       <c r="D32" s="19">
         <v>2</v>
@@ -2629,8 +2686,8 @@
       <c r="A33" s="19">
         <v>660001</v>
       </c>
-      <c r="B33" s="33" t="s">
-        <v>167</v>
+      <c r="B33" s="34" t="s">
+        <v>165</v>
       </c>
       <c r="D33" s="19">
         <v>2</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_auto_release_v8【迷宫-技能-自动释放技能】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_auto_release_v8【迷宫-技能-自动释放技能】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F6253B5-5B65-4568-A80D-816F45BA1DD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06F28D94-5C3F-4C2D-87AB-3D63A91CCE28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_auto_release_v8" sheetId="7" r:id="rId1"/>
@@ -2539,7 +2539,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="19">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J29" s="19" t="s">
         <v>0</v>

--- a/servers/maze_main_server/conf.d/data/maze_skill_auto_release_v8【迷宫-技能-自动释放技能】.xlsx
+++ b/servers/maze_main_server/conf.d/data/maze_skill_auto_release_v8【迷宫-技能-自动释放技能】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06F28D94-5C3F-4C2D-87AB-3D63A91CCE28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F6253B5-5B65-4568-A80D-816F45BA1DD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_auto_release_v8" sheetId="7" r:id="rId1"/>
@@ -2539,7 +2539,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J29" s="19" t="s">
         <v>0</v>
